--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -7682,7 +7682,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -7682,7 +7682,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5908,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6294,7 +6294,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251221_201423.xlsx
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
